--- a/data/trans_orig/P16A12-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A12-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19204</t>
+          <t>19227</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34103</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253806</t>
+          <t>253783</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266390</t>
+          <t>266452</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>243167</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255713</t>
+          <t>255058</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>499745</t>
+          <t>500766</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>518699</t>
+          <t>519208</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17983</t>
+          <t>18089</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39399</t>
+          <t>37881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29962</t>
+          <t>30265</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54669</t>
+          <t>53438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51653</t>
+          <t>52787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83861</t>
+          <t>84619</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>453676</t>
+          <t>455194</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>475092</t>
+          <t>474986</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>449280</t>
+          <t>450511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>473987</t>
+          <t>473684</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>913163</t>
+          <t>912405</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>945371</t>
+          <t>944237</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>24865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34864</t>
+          <t>34557</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28377</t>
+          <t>29557</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53560</t>
+          <t>54243</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>293680</t>
+          <t>293981</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>309334</t>
+          <t>310024</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>300548</t>
+          <t>300855</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>318863</t>
+          <t>319300</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>600698</t>
+          <t>600015</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>625881</t>
+          <t>624701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>12135</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27329</t>
+          <t>28363</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11235</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27720</t>
+          <t>26797</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26730</t>
+          <t>26547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48449</t>
+          <t>46697</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>331342</t>
+          <t>330308</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>347531</t>
+          <t>346536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343736</t>
+          <t>344659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>360221</t>
+          <t>360035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>681678</t>
+          <t>683430</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>703397</t>
+          <t>703580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16070</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27958</t>
+          <t>28002</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39153</t>
+          <t>39672</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>187238</t>
+          <t>187291</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198116</t>
+          <t>198122</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179710</t>
+          <t>179666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>196988</t>
+          <t>197015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>371823</t>
+          <t>371304</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392307</t>
+          <t>392779</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24229</t>
+          <t>25392</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17437</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16098</t>
+          <t>17378</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35358</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246582</t>
+          <t>245419</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261921</t>
+          <t>261778</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260707</t>
+          <t>260943</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273038</t>
+          <t>273913</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>513597</t>
+          <t>510584</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532857</t>
+          <t>531577</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30265</t>
+          <t>30354</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54839</t>
+          <t>56598</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29655</t>
+          <t>29605</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54619</t>
+          <t>53536</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66785</t>
+          <t>67743</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100646</t>
+          <t>101199</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>560188</t>
+          <t>558429</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>584762</t>
+          <t>584673</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>583600</t>
+          <t>584683</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>608564</t>
+          <t>608614</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1152600</t>
+          <t>1152047</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1186461</t>
+          <t>1185503</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32209</t>
+          <t>33737</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57167</t>
+          <t>58014</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31778</t>
+          <t>31801</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58941</t>
+          <t>58037</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71041</t>
+          <t>69412</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>107119</t>
+          <t>106490</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>685610</t>
+          <t>684763</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>710568</t>
+          <t>709040</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>724570</t>
+          <t>725474</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>751733</t>
+          <t>751710</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1419169</t>
+          <t>1419798</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1455247</t>
+          <t>1456876</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>158970</t>
+          <t>159289</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>209442</t>
+          <t>209717</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>177613</t>
+          <t>178922</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>237097</t>
+          <t>234057</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>349023</t>
+          <t>352733</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>424353</t>
+          <t>426803</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3066083</t>
+          <t>3065808</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3116555</t>
+          <t>3116236</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3142100</t>
+          <t>3145140</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3201584</t>
+          <t>3200275</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6230369</t>
+          <t>6227919</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6305699</t>
+          <t>6301989</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2012 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11727</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>29007</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28506</t>
+          <t>27634</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27164</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52431</t>
+          <t>51484</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262242</t>
+          <t>263188</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>280468</t>
+          <t>280916</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252774</t>
+          <t>253646</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269907</t>
+          <t>270713</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>521043</t>
+          <t>521990</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>546310</t>
+          <t>546937</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49046</t>
+          <t>49423</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44553</t>
+          <t>44509</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73786</t>
+          <t>73445</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75545</t>
+          <t>73342</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114816</t>
+          <t>111273</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456481</t>
+          <t>456104</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>480893</t>
+          <t>480807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448945</t>
+          <t>449286</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>478178</t>
+          <t>478222</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>913442</t>
+          <t>916985</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952713</t>
+          <t>954916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>22934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45981</t>
+          <t>45727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24214</t>
+          <t>25238</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48953</t>
+          <t>48920</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54913</t>
+          <t>53752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86660</t>
+          <t>85480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277135</t>
+          <t>277389</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301043</t>
+          <t>300182</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>292067</t>
+          <t>292100</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>316806</t>
+          <t>315782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>577476</t>
+          <t>578656</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>609223</t>
+          <t>610384</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>14643</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33165</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21916</t>
+          <t>22894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43537</t>
+          <t>44521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40794</t>
+          <t>41389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70258</t>
+          <t>68609</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340817</t>
+          <t>341793</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359975</t>
+          <t>359339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>344437</t>
+          <t>343453</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366058</t>
+          <t>365080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>691698</t>
+          <t>693347</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>721162</t>
+          <t>720567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11376</t>
+          <t>11367</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28926</t>
+          <t>29745</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>17390</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37346</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33140</t>
+          <t>33378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58779</t>
+          <t>60465</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183692</t>
+          <t>182873</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201242</t>
+          <t>201251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182245</t>
+          <t>182456</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202324</t>
+          <t>202201</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>373430</t>
+          <t>371744</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>399069</t>
+          <t>398831</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28091</t>
+          <t>27724</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20024</t>
+          <t>20845</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40791</t>
+          <t>42445</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35722</t>
+          <t>36549</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61275</t>
+          <t>61848</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245890</t>
+          <t>246257</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261899</t>
+          <t>262541</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>238349</t>
+          <t>236695</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>259116</t>
+          <t>258295</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>491846</t>
+          <t>491273</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>517399</t>
+          <t>516572</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40479</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69868</t>
+          <t>69984</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43522</t>
+          <t>43888</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73221</t>
+          <t>73182</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89874</t>
+          <t>92134</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>130696</t>
+          <t>133766</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>592920</t>
+          <t>592804</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>622309</t>
+          <t>622399</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>620632</t>
+          <t>620671</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>650331</t>
+          <t>649965</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1225945</t>
+          <t>1222875</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1266767</t>
+          <t>1264507</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35711</t>
+          <t>35868</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>63823</t>
+          <t>65397</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>33906</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60403</t>
+          <t>61020</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>76110</t>
+          <t>74855</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>115413</t>
+          <t>116372</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>713149</t>
+          <t>711575</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>741261</t>
+          <t>741104</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>761117</t>
+          <t>760500</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>788367</t>
+          <t>787614</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1483079</t>
+          <t>1482120</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1522382</t>
+          <t>1523637</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>219446</t>
+          <t>221138</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>282832</t>
+          <t>284347</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>269319</t>
+          <t>266721</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>335355</t>
+          <t>333511</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>502682</t>
+          <t>502880</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>599412</t>
+          <t>592595</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3138347</t>
+          <t>3136832</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3201733</t>
+          <t>3200041</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3211755</t>
+          <t>3213599</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3277791</t>
+          <t>3280389</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6368877</t>
+          <t>6375694</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6465607</t>
+          <t>6465409</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28680</t>
+          <t>30087</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>18431</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42188</t>
+          <t>41542</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265081</t>
+          <t>263674</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281798</t>
+          <t>281499</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270683</t>
+          <t>270272</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283397</t>
+          <t>283418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540276</t>
+          <t>540922</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562226</t>
+          <t>562222</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24185</t>
+          <t>24262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47247</t>
+          <t>46878</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42365</t>
+          <t>40965</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72297</t>
+          <t>69188</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71193</t>
+          <t>70542</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109963</t>
+          <t>108391</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>455328</t>
+          <t>455697</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>478390</t>
+          <t>478313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>450787</t>
+          <t>453896</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480719</t>
+          <t>482119</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>915696</t>
+          <t>917268</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>954466</t>
+          <t>955117</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,12%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>21880</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33038</t>
+          <t>32022</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25065</t>
+          <t>23837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49211</t>
+          <t>46919</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297256</t>
+          <t>296685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310426</t>
+          <t>310831</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>303271</t>
+          <t>304287</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323004</t>
+          <t>323168</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>605663</t>
+          <t>607955</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>629809</t>
+          <t>631037</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34586</t>
+          <t>33665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60561</t>
+          <t>59861</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37035</t>
+          <t>37766</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56681</t>
+          <t>56023</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90240</t>
+          <t>88601</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>309403</t>
+          <t>310103</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>335378</t>
+          <t>336299</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>350248</t>
+          <t>349517</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>370221</t>
+          <t>370254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>667007</t>
+          <t>668646</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>700566</t>
+          <t>701224</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21777</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>13636</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30417</t>
+          <t>30139</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>24168</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>46784</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>189444</t>
+          <t>190353</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203593</t>
+          <t>204019</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188170</t>
+          <t>188448</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204879</t>
+          <t>204951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384147</t>
+          <t>383024</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>405448</t>
+          <t>405640</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25768</t>
+          <t>27308</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10560</t>
+          <t>10842</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28618</t>
+          <t>29291</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25405</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49775</t>
+          <t>50274</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237355</t>
+          <t>235815</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252547</t>
+          <t>252145</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244497</t>
+          <t>243824</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262555</t>
+          <t>262273</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>486463</t>
+          <t>485964</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>510833</t>
+          <t>511244</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55588</t>
+          <t>55902</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91110</t>
+          <t>87908</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40946</t>
+          <t>40092</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69877</t>
+          <t>72752</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>104249</t>
+          <t>105031</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150812</t>
+          <t>150830</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>565448</t>
+          <t>568650</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>600970</t>
+          <t>600656</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>621417</t>
+          <t>618542</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>650348</t>
+          <t>651202</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1197040</t>
+          <t>1197022</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1243603</t>
+          <t>1242821</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,21%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55618</t>
+          <t>54798</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86808</t>
+          <t>85879</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,49 +9795,49 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>11,03%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>72746</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>56765</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>92131</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
           <t>11,15%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>72746</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>56049</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>91430</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>133</t>
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118067</t>
+          <t>121106</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>167963</t>
+          <t>165098</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>691775</t>
+          <t>692704</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>722965</t>
+          <t>723785</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,47 +9908,47 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>88,97%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>753421</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>734036</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>769402</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>91,19%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>88,85%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>92,86%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>753421</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>734737</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>770118</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>91,19%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>88,93%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1436787</t>
+          <t>1439652</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1486683</t>
+          <t>1483644</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>253157</t>
+          <t>252972</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>316850</t>
+          <t>316276</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,82 +10138,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>277943</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>247421</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>316075</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>8,92%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>561750</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>517427</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>610129</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>7,46%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>277943</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>246106</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>313433</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>561750</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>517317</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>608821</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3077500</t>
+          <t>3078074</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3141193</t>
+          <t>3141378</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3231109</t>
+          <t>3228467</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3298436</t>
+          <t>3297121</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6330071</t>
+          <t>6328763</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6421575</t>
+          <t>6421465</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22525</t>
+          <t>21866</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41628</t>
+          <t>42255</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27993</t>
+          <t>28265</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41306</t>
+          <t>42281</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63817</t>
+          <t>64488</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269815</t>
+          <t>269188</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288918</t>
+          <t>289577</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261642</t>
+          <t>261370</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273790</t>
+          <t>273635</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>537260</t>
+          <t>536589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>559771</t>
+          <t>558796</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23418</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47115</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30410</t>
+          <t>30497</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49516</t>
+          <t>51015</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60161</t>
+          <t>59377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90234</t>
+          <t>90494</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>470278</t>
+          <t>469519</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>493975</t>
+          <t>494390</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464209</t>
+          <t>462710</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>483315</t>
+          <t>483228</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>940884</t>
+          <t>940624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>970957</t>
+          <t>971741</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27419</t>
+          <t>27676</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45498</t>
+          <t>45641</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27968</t>
+          <t>27765</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45281</t>
+          <t>45093</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60563</t>
+          <t>59258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85972</t>
+          <t>84367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270552</t>
+          <t>270409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>288631</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>303847</t>
+          <t>304035</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321160</t>
+          <t>321363</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>579206</t>
+          <t>580811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>604615</t>
+          <t>605920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19347</t>
+          <t>19148</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36856</t>
+          <t>37296</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35863</t>
+          <t>35424</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37596</t>
+          <t>37552</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66024</t>
+          <t>68006</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275701</t>
+          <t>275261</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>293210</t>
+          <t>293409</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>439855</t>
+          <t>440294</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>459968</t>
+          <t>460044</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>722250</t>
+          <t>720268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>750678</t>
+          <t>750722</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>13174</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>26400</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19884</t>
+          <t>19697</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31345</t>
+          <t>31721</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36163</t>
+          <t>35748</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52497</t>
+          <t>52613</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153930</t>
+          <t>152342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165922</t>
+          <t>165568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177311</t>
+          <t>176935</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188772</t>
+          <t>188959</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>334901</t>
+          <t>334785</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>351235</t>
+          <t>351650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30741</t>
+          <t>30823</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48063</t>
+          <t>49022</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>21545</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33619</t>
+          <t>34697</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55846</t>
+          <t>54586</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77244</t>
+          <t>75767</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221573</t>
+          <t>220614</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238895</t>
+          <t>238813</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223437</t>
+          <t>222359</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>236062</t>
+          <t>235511</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>449448</t>
+          <t>450925</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>470846</t>
+          <t>472106</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38909</t>
+          <t>38891</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64723</t>
+          <t>64798</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17320</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51013</t>
+          <t>51691</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55232</t>
+          <t>55857</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108317</t>
+          <t>109464</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>559556</t>
+          <t>559481</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>585370</t>
+          <t>585388</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>798252</t>
+          <t>797574</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>831945</t>
+          <t>832777</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1365227</t>
+          <t>1364080</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1418312</t>
+          <t>1417687</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>20882</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>68854</t>
+          <t>69786</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34568</t>
+          <t>34267</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52996</t>
+          <t>52406</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55288</t>
+          <t>52625</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>111144</t>
+          <t>111620</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>859866</t>
+          <t>858934</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>908898</t>
+          <t>907838</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>661855</t>
+          <t>662445</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>680283</t>
+          <t>680584</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1532428</t>
+          <t>1531952</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1588284</t>
+          <t>1590947</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>222751</t>
+          <t>211549</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>319679</t>
+          <t>319523</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>203062</t>
+          <t>207611</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>280081</t>
+          <t>281874</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>470477</t>
+          <t>461231</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>588927</t>
+          <t>586496</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3139141</t>
+          <t>3139297</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3236069</t>
+          <t>3247271</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3377952</t>
+          <t>3376159</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3454971</t>
+          <t>3450422</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6527926</t>
+          <t>6530357</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6646376</t>
+          <t>6655622</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A12-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A12-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19227</t>
+          <t>19317</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>18731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33082</t>
+          <t>32883</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253783</t>
+          <t>253693</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266452</t>
+          <t>266527</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242107</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255058</t>
+          <t>255593</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>500766</t>
+          <t>500965</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>519208</t>
+          <t>519726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>17621</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37881</t>
+          <t>38582</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30265</t>
+          <t>28782</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53438</t>
+          <t>52964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52787</t>
+          <t>51644</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84619</t>
+          <t>84142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>455194</t>
+          <t>454493</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>474986</t>
+          <t>475454</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>450511</t>
+          <t>450985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>473684</t>
+          <t>475167</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>912405</t>
+          <t>912882</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>944237</t>
+          <t>945380</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24865</t>
+          <t>23596</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>16279</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34557</t>
+          <t>35585</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29557</t>
+          <t>30479</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54243</t>
+          <t>53237</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>293981</t>
+          <t>295250</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310024</t>
+          <t>309372</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>300855</t>
+          <t>299827</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319300</t>
+          <t>319133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>600015</t>
+          <t>601021</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>624701</t>
+          <t>623779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12135</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28363</t>
+          <t>27471</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26797</t>
+          <t>26489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26547</t>
+          <t>25817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46697</t>
+          <t>48846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>330308</t>
+          <t>331200</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>346536</t>
+          <t>347587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>344659</t>
+          <t>344967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>360035</t>
+          <t>360223</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>683430</t>
+          <t>681281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>703580</t>
+          <t>704310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>28393</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>19126</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39672</t>
+          <t>39424</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>187291</t>
+          <t>186234</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198122</t>
+          <t>198057</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179666</t>
+          <t>179275</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197015</t>
+          <t>196997</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>371304</t>
+          <t>371552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392779</t>
+          <t>391850</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25392</t>
+          <t>24980</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17201</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17378</t>
+          <t>15576</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>36198</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245419</t>
+          <t>245831</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261778</t>
+          <t>261947</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260943</t>
+          <t>261088</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273913</t>
+          <t>273919</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>510584</t>
+          <t>512757</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>531577</t>
+          <t>533379</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30354</t>
+          <t>31771</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56598</t>
+          <t>55884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29605</t>
+          <t>29955</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53536</t>
+          <t>54665</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67743</t>
+          <t>66243</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>101199</t>
+          <t>99336</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>558429</t>
+          <t>559143</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>584673</t>
+          <t>583256</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>584683</t>
+          <t>583554</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>608614</t>
+          <t>608264</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1152047</t>
+          <t>1153910</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1185503</t>
+          <t>1187003</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>32234</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58014</t>
+          <t>57925</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31801</t>
+          <t>31630</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58037</t>
+          <t>58656</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69412</t>
+          <t>71531</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106490</t>
+          <t>107045</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>684763</t>
+          <t>684852</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>709040</t>
+          <t>710543</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>725474</t>
+          <t>724855</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>751710</t>
+          <t>751881</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1419798</t>
+          <t>1419243</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1456876</t>
+          <t>1454757</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>159289</t>
+          <t>158228</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>209717</t>
+          <t>209691</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>178922</t>
+          <t>177006</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>234057</t>
+          <t>231537</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>352733</t>
+          <t>352579</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>426803</t>
+          <t>428694</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3065808</t>
+          <t>3065834</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3116236</t>
+          <t>3117297</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3145140</t>
+          <t>3147660</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3200275</t>
+          <t>3202191</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6227919</t>
+          <t>6226028</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6301989</t>
+          <t>6302143</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29007</t>
+          <t>30052</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27634</t>
+          <t>28543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26537</t>
+          <t>25347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51484</t>
+          <t>50872</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263188</t>
+          <t>262143</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>280916</t>
+          <t>280563</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253646</t>
+          <t>252737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270713</t>
+          <t>269377</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>521990</t>
+          <t>522602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>546937</t>
+          <t>548127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24720</t>
+          <t>23535</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49423</t>
+          <t>47435</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44509</t>
+          <t>43398</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73445</t>
+          <t>72227</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>75051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>113257</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456104</t>
+          <t>458092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>480807</t>
+          <t>481992</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>449286</t>
+          <t>450504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>478222</t>
+          <t>479333</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>916985</t>
+          <t>915001</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>954916</t>
+          <t>953207</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22934</t>
+          <t>23423</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45727</t>
+          <t>46137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>24893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48920</t>
+          <t>49032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53752</t>
+          <t>54347</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85480</t>
+          <t>86144</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277389</t>
+          <t>276979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>300182</t>
+          <t>299693</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>292100</t>
+          <t>291988</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315782</t>
+          <t>316127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>578656</t>
+          <t>577992</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>610384</t>
+          <t>609789</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32189</t>
+          <t>32301</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22894</t>
+          <t>22169</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44521</t>
+          <t>43595</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41389</t>
+          <t>40605</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68609</t>
+          <t>69827</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341793</t>
+          <t>341681</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359339</t>
+          <t>359622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343453</t>
+          <t>344379</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>365080</t>
+          <t>365805</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>693347</t>
+          <t>692129</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>720567</t>
+          <t>721351</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29745</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17390</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37135</t>
+          <t>36624</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33378</t>
+          <t>33164</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60465</t>
+          <t>58440</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>182873</t>
+          <t>184163</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201251</t>
+          <t>201551</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182456</t>
+          <t>182967</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202201</t>
+          <t>202188</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>371744</t>
+          <t>373769</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>398831</t>
+          <t>399045</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,33%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27724</t>
+          <t>28222</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20845</t>
+          <t>20042</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42445</t>
+          <t>41514</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36549</t>
+          <t>34634</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61848</t>
+          <t>62743</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246257</t>
+          <t>245759</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262541</t>
+          <t>262758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236695</t>
+          <t>237626</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>258295</t>
+          <t>259098</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>491273</t>
+          <t>490378</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>516572</t>
+          <t>518487</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>40957</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69984</t>
+          <t>69748</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43888</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73182</t>
+          <t>71826</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92134</t>
+          <t>91612</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133766</t>
+          <t>131988</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>592804</t>
+          <t>593040</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>622399</t>
+          <t>621831</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>620671</t>
+          <t>622027</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>649965</t>
+          <t>650658</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1222875</t>
+          <t>1224653</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1264507</t>
+          <t>1265029</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35868</t>
+          <t>35385</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65397</t>
+          <t>64008</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33906</t>
+          <t>32615</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61020</t>
+          <t>59078</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74855</t>
+          <t>76836</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>116372</t>
+          <t>114732</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>711575</t>
+          <t>712964</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>741104</t>
+          <t>741587</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>760500</t>
+          <t>762442</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>787614</t>
+          <t>788905</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1482120</t>
+          <t>1483760</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1523637</t>
+          <t>1521656</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>221138</t>
+          <t>218039</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>284347</t>
+          <t>282352</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>266721</t>
+          <t>267237</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>333511</t>
+          <t>332385</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>502880</t>
+          <t>506456</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>592595</t>
+          <t>597037</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3136832</t>
+          <t>3138827</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3200041</t>
+          <t>3203140</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3213599</t>
+          <t>3214725</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3280389</t>
+          <t>3279873</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6375694</t>
+          <t>6371252</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6465409</t>
+          <t>6461833</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30087</t>
+          <t>30438</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18431</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41542</t>
+          <t>42952</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263674</t>
+          <t>263323</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281499</t>
+          <t>282076</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270272</t>
+          <t>270585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283418</t>
+          <t>283675</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540922</t>
+          <t>539512</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562222</t>
+          <t>561540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24262</t>
+          <t>24729</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46878</t>
+          <t>47042</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40965</t>
+          <t>40119</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69188</t>
+          <t>69146</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70542</t>
+          <t>71225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108391</t>
+          <t>108626</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>455697</t>
+          <t>455533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>478313</t>
+          <t>477846</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>453896</t>
+          <t>453938</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>482119</t>
+          <t>482965</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>917268</t>
+          <t>917033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>955117</t>
+          <t>954434</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21880</t>
+          <t>21373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13141</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32022</t>
+          <t>31704</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23837</t>
+          <t>24658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46919</t>
+          <t>47533</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296685</t>
+          <t>297192</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310831</t>
+          <t>309954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>304287</t>
+          <t>304605</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323168</t>
+          <t>323089</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>607955</t>
+          <t>607341</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>631037</t>
+          <t>630216</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33665</t>
+          <t>33393</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59861</t>
+          <t>58371</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>17630</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37766</t>
+          <t>37382</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56023</t>
+          <t>57702</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88601</t>
+          <t>90541</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>310103</t>
+          <t>311593</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>336299</t>
+          <t>336571</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349517</t>
+          <t>349901</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>370254</t>
+          <t>369653</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>668646</t>
+          <t>666706</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>701224</t>
+          <t>699545</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,38%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20868</t>
+          <t>20838</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13636</t>
+          <t>12978</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>29968</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24168</t>
+          <t>23257</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46784</t>
+          <t>45160</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>190353</t>
+          <t>190383</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204019</t>
+          <t>203971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188448</t>
+          <t>188619</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204951</t>
+          <t>205609</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383024</t>
+          <t>384648</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>405640</t>
+          <t>406551</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10978</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27308</t>
+          <t>25993</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10842</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29291</t>
+          <t>29025</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24994</t>
+          <t>24809</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50274</t>
+          <t>47532</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235815</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252145</t>
+          <t>251987</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243824</t>
+          <t>244090</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262273</t>
+          <t>262709</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>485964</t>
+          <t>488706</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>511244</t>
+          <t>511429</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55902</t>
+          <t>54963</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87908</t>
+          <t>87734</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40092</t>
+          <t>40116</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72752</t>
+          <t>71544</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>105031</t>
+          <t>104977</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150830</t>
+          <t>150029</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>568650</t>
+          <t>568824</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>600656</t>
+          <t>601595</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>618542</t>
+          <t>619750</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>651202</t>
+          <t>651178</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1197022</t>
+          <t>1197823</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1242821</t>
+          <t>1242875</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54798</t>
+          <t>56364</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85879</t>
+          <t>85202</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56765</t>
+          <t>57239</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92131</t>
+          <t>92834</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>121106</t>
+          <t>120597</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>165098</t>
+          <t>166231</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>692704</t>
+          <t>693381</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>723785</t>
+          <t>722219</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>734036</t>
+          <t>733333</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>769402</t>
+          <t>768928</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1439652</t>
+          <t>1438519</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1483644</t>
+          <t>1484153</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>252972</t>
+          <t>252521</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>316276</t>
+          <t>313703</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>247421</t>
+          <t>245451</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>316075</t>
+          <t>315598</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>517427</t>
+          <t>517451</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>610129</t>
+          <t>605904</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3078074</t>
+          <t>3080647</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3141378</t>
+          <t>3141829</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3228467</t>
+          <t>3228944</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3297121</t>
+          <t>3299091</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6328763</t>
+          <t>6332988</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6421465</t>
+          <t>6421441</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30724</t>
+          <t>31244</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21866</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42255</t>
+          <t>42063</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>23730</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28265</t>
+          <t>30539</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>52016</t>
+          <t>54974</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42281</t>
+          <t>43794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64488</t>
+          <t>67449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>280719</t>
+          <t>287601</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269188</t>
+          <t>276782</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289577</t>
+          <t>296361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>268344</t>
+          <t>292331</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261370</t>
+          <t>285522</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273635</t>
+          <t>298187</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>549061</t>
+          <t>579932</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>536589</t>
+          <t>567457</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>558796</t>
+          <t>591112</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34421</t>
+          <t>34725</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23003</t>
+          <t>23515</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>46841</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39507</t>
+          <t>41174</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30497</t>
+          <t>31680</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51015</t>
+          <t>51557</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>73929</t>
+          <t>75898</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59377</t>
+          <t>62957</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90494</t>
+          <t>92766</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>482972</t>
+          <t>494935</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>469519</t>
+          <t>482819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494390</t>
+          <t>506145</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>474218</t>
+          <t>504039</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>462710</t>
+          <t>493656</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>483228</t>
+          <t>513533</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>957189</t>
+          <t>998975</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>940624</t>
+          <t>982107</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>971741</t>
+          <t>1011916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>35790</t>
+          <t>35403</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27676</t>
+          <t>27389</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45641</t>
+          <t>45362</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>36330</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27765</t>
+          <t>28841</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45093</t>
+          <t>45476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,22 +11453,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>71792</t>
+          <t>71733</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59258</t>
+          <t>59886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84367</t>
+          <t>84419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>280260</t>
+          <t>280590</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270409</t>
+          <t>270631</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>288604</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>313126</t>
+          <t>320051</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>304035</t>
+          <t>310905</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321363</t>
+          <t>327540</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,27 +11566,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>593386</t>
+          <t>600642</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>580811</t>
+          <t>587956</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>605920</t>
+          <t>612489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26774</t>
+          <t>31804</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19148</t>
+          <t>22723</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37296</t>
+          <t>43391</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25724</t>
+          <t>27229</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15674</t>
+          <t>20904</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35424</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>52498</t>
+          <t>59033</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37552</t>
+          <t>47902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68006</t>
+          <t>73612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>285783</t>
+          <t>341341</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275261</t>
+          <t>329754</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>293409</t>
+          <t>350422</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>449994</t>
+          <t>394732</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>440294</t>
+          <t>386488</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>460044</t>
+          <t>401057</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>735776</t>
+          <t>736074</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>720268</t>
+          <t>721495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>750722</t>
+          <t>747205</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>19245</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13174</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26400</t>
+          <t>26242</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25384</t>
+          <t>26456</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>20947</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31721</t>
+          <t>32803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>43629</t>
+          <t>45701</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35748</t>
+          <t>36729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52613</t>
+          <t>55021</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>160497</t>
+          <t>186420</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152342</t>
+          <t>179423</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165568</t>
+          <t>192264</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>183272</t>
+          <t>200759</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176935</t>
+          <t>194412</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188959</t>
+          <t>206268</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>343769</t>
+          <t>387178</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>334785</t>
+          <t>377858</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>351650</t>
+          <t>396150</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38642</t>
+          <t>38821</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30823</t>
+          <t>30882</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49022</t>
+          <t>47567</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,67 +12447,67 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>27727</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34697</t>
+          <t>35189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>8,19%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>13,34%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>66548</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>56283</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>77193</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>10,53%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>13,5%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>65709</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>54586</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>75767</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>10,36%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>230994</t>
+          <t>231886</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220614</t>
+          <t>223140</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238813</t>
+          <t>239825</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,67 +12560,67 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>229990</t>
+          <t>236023</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>222359</t>
+          <t>228561</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>235511</t>
+          <t>242161</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
+          <t>89,49%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>86,66%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>91,81%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>467909</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>457264</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>478174</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>87,55%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>85,56%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>89,47%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>86,5%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>91,62%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>460983</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>450925</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>472106</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>87,52%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>85,61%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>50799</t>
+          <t>62489</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38891</t>
+          <t>47753</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64798</t>
+          <t>76799</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>35959</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>34415</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51691</t>
+          <t>56262</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>86759</t>
+          <t>106692</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55857</t>
+          <t>89207</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>109464</t>
+          <t>125382</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>573480</t>
+          <t>657198</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>559481</t>
+          <t>642888</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>585388</t>
+          <t>671934</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>813306</t>
+          <t>727854</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>797574</t>
+          <t>715795</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>832777</t>
+          <t>737642</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1386785</t>
+          <t>1385052</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1364080</t>
+          <t>1366362</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1417687</t>
+          <t>1402537</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>46712</t>
+          <t>52426</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20882</t>
+          <t>40457</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69786</t>
+          <t>66392</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>42783</t>
+          <t>50398</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34267</t>
+          <t>39137</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52406</t>
+          <t>62275</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>89495</t>
+          <t>102824</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52625</t>
+          <t>86988</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>111620</t>
+          <t>121565</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>882008</t>
+          <t>745646</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>858934</t>
+          <t>731680</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>907838</t>
+          <t>757615</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>672068</t>
+          <t>779608</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>662445</t>
+          <t>767731</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>680584</t>
+          <t>790869</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1554077</t>
+          <t>1525254</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1531952</t>
+          <t>1506513</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1590947</t>
+          <t>1541090</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,69 +13441,69 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>282108</t>
+          <t>306157</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>211549</t>
+          <t>277521</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>319523</t>
+          <t>339357</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>8,67%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>9,61%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>277246</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>254897</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>304505</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
           <t>8,16%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>253717</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>207611</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>281874</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>927</t>
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>535825</t>
+          <t>583403</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>461231</t>
+          <t>545388</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>586496</t>
+          <t>624473</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -13554,67 +13554,67 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3176712</t>
+          <t>3225618</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3139297</t>
+          <t>3192418</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3247271</t>
+          <t>3254254</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>91,33%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>90,39%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>4838</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3455399</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3428140</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3477748</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>92,57%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>91,84%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>90,76%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>93,88%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>4838</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3404316</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3376159</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3450422</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>92,29%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6581028</t>
+          <t>6681016</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6530357</t>
+          <t>6639946</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6655622</t>
+          <t>6719031</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
